--- a/artfynd/A 15836-2024 artfynd.xlsx
+++ b/artfynd/A 15836-2024 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117940323</v>
+        <v>117939351</v>
       </c>
       <c r="B7" t="n">
-        <v>100007</v>
+        <v>41164</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582162</v>
+        <v>582159</v>
       </c>
       <c r="R7" t="n">
-        <v>6989239</v>
+        <v>6989231</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117939351</v>
+        <v>117940323</v>
       </c>
       <c r="B8" t="n">
-        <v>41164</v>
+        <v>100007</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100453</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582159</v>
+        <v>582162</v>
       </c>
       <c r="R8" t="n">
-        <v>6989231</v>
+        <v>6989239</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 15836-2024 artfynd.xlsx
+++ b/artfynd/A 15836-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117940714</v>
+        <v>117940604</v>
       </c>
       <c r="B2" t="n">
         <v>100007</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582214</v>
+        <v>582240</v>
       </c>
       <c r="R2" t="n">
-        <v>6989217</v>
+        <v>6989227</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117940181</v>
+        <v>117940358</v>
       </c>
       <c r="B3" t="n">
         <v>100007</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582118</v>
+        <v>582144</v>
       </c>
       <c r="R3" t="n">
-        <v>6989264</v>
+        <v>6989238</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117940604</v>
+        <v>117939351</v>
       </c>
       <c r="B4" t="n">
-        <v>100007</v>
+        <v>41164</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582240</v>
+        <v>582159</v>
       </c>
       <c r="R4" t="n">
-        <v>6989227</v>
+        <v>6989231</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117940958</v>
+        <v>117940646</v>
       </c>
       <c r="B5" t="n">
-        <v>41164</v>
+        <v>100007</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100453</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582158</v>
+        <v>582233</v>
       </c>
       <c r="R5" t="n">
-        <v>6989278</v>
+        <v>6989261</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117940358</v>
+        <v>117940714</v>
       </c>
       <c r="B6" t="n">
         <v>100007</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582144</v>
+        <v>582214</v>
       </c>
       <c r="R6" t="n">
-        <v>6989238</v>
+        <v>6989217</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117939351</v>
+        <v>117940323</v>
       </c>
       <c r="B7" t="n">
-        <v>41164</v>
+        <v>100007</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100453</v>
+        <v>222771</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582159</v>
+        <v>582162</v>
       </c>
       <c r="R7" t="n">
-        <v>6989231</v>
+        <v>6989239</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117940323</v>
+        <v>117940181</v>
       </c>
       <c r="B8" t="n">
         <v>100007</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582162</v>
+        <v>582118</v>
       </c>
       <c r="R8" t="n">
-        <v>6989239</v>
+        <v>6989264</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117940646</v>
+        <v>117940958</v>
       </c>
       <c r="B9" t="n">
-        <v>100007</v>
+        <v>41164</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582233</v>
+        <v>582158</v>
       </c>
       <c r="R9" t="n">
-        <v>6989261</v>
+        <v>6989278</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 15836-2024 artfynd.xlsx
+++ b/artfynd/A 15836-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117940604</v>
+        <v>117940181</v>
       </c>
       <c r="B2" t="n">
-        <v>100007</v>
+        <v>100009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582240</v>
+        <v>582118</v>
       </c>
       <c r="R2" t="n">
-        <v>6989227</v>
+        <v>6989264</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117940358</v>
+        <v>117940323</v>
       </c>
       <c r="B3" t="n">
-        <v>100007</v>
+        <v>100009</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582144</v>
+        <v>582162</v>
       </c>
       <c r="R3" t="n">
-        <v>6989238</v>
+        <v>6989239</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117939351</v>
+        <v>117940714</v>
       </c>
       <c r="B4" t="n">
-        <v>41164</v>
+        <v>100009</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100453</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582159</v>
+        <v>582214</v>
       </c>
       <c r="R4" t="n">
-        <v>6989231</v>
+        <v>6989217</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117940646</v>
+        <v>117940958</v>
       </c>
       <c r="B5" t="n">
-        <v>100007</v>
+        <v>41164</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582233</v>
+        <v>582158</v>
       </c>
       <c r="R5" t="n">
-        <v>6989261</v>
+        <v>6989278</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117940714</v>
+        <v>117940358</v>
       </c>
       <c r="B6" t="n">
-        <v>100007</v>
+        <v>100009</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582214</v>
+        <v>582144</v>
       </c>
       <c r="R6" t="n">
-        <v>6989217</v>
+        <v>6989238</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117940323</v>
+        <v>117940604</v>
       </c>
       <c r="B7" t="n">
-        <v>100007</v>
+        <v>100009</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582162</v>
+        <v>582240</v>
       </c>
       <c r="R7" t="n">
-        <v>6989239</v>
+        <v>6989227</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117940181</v>
+        <v>117940646</v>
       </c>
       <c r="B8" t="n">
-        <v>100007</v>
+        <v>100009</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582118</v>
+        <v>582233</v>
       </c>
       <c r="R8" t="n">
-        <v>6989264</v>
+        <v>6989261</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117940958</v>
+        <v>117939351</v>
       </c>
       <c r="B9" t="n">
         <v>41164</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582158</v>
+        <v>582159</v>
       </c>
       <c r="R9" t="n">
-        <v>6989278</v>
+        <v>6989231</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1494,7 +1494,7 @@
         <v>117958577</v>
       </c>
       <c r="B10" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>117958501</v>
       </c>
       <c r="B11" t="n">
-        <v>90510</v>
+        <v>90512</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 15836-2024 artfynd.xlsx
+++ b/artfynd/A 15836-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117940358</v>
+        <v>117958501</v>
       </c>
       <c r="B2" t="n">
-        <v>100017</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bispgården (Bispgården), Jmt</t>
+          <t>Bispgården, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582144</v>
+        <v>582151</v>
       </c>
       <c r="R2" t="n">
-        <v>6989238</v>
+        <v>6989251</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,65 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117940604</v>
+        <v>117958577</v>
       </c>
       <c r="B3" t="n">
-        <v>100017</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bispgården (Bispgården), Jmt</t>
+          <t>Bispgården, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582240</v>
+        <v>582146</v>
       </c>
       <c r="R3" t="n">
-        <v>6989227</v>
+        <v>6989221</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,12 +882,7 @@
         <v>117939351</v>
       </c>
       <c r="B4" t="n">
-        <v>41164</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,7 +910,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bispgården (Bispgården), Jmt</t>
+          <t>Bispgården, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -981,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117940958</v>
+        <v>117939819</v>
       </c>
       <c r="B5" t="n">
-        <v>41164</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41670</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,17 +1007,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bispgården (Bispgården), Jmt</t>
+          <t>Bispgården, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582158</v>
+        <v>582108</v>
       </c>
       <c r="R5" t="n">
-        <v>6989278</v>
+        <v>6989202</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,53 +1073,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117940646</v>
+        <v>117940958</v>
       </c>
       <c r="B6" t="n">
-        <v>100017</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41670</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bispgården (Bispgården), Jmt</t>
+          <t>Bispgården, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582233</v>
+        <v>582158</v>
       </c>
       <c r="R6" t="n">
-        <v>6989261</v>
+        <v>6989278</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,15 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117940181</v>
+        <v>118622632</v>
       </c>
       <c r="B7" t="n">
-        <v>100017</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,37 +1181,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>105947</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Större aspvedbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Saperda carcharias</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bispgården (Bispgården), Jmt</t>
+          <t>Bispgården, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582118</v>
+        <v>582261</v>
       </c>
       <c r="R7" t="n">
-        <v>6989264</v>
+        <v>6989337</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1235,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,27 +1255,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Esbjörn Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Esbjörn Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117940323</v>
+        <v>117939659</v>
       </c>
       <c r="B8" t="n">
-        <v>100017</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,14 +1298,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bispgården (Bispgården), Jmt</t>
+          <t>Bispgården, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582162</v>
+        <v>582074</v>
       </c>
       <c r="R8" t="n">
-        <v>6989239</v>
+        <v>6989230</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,15 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117940714</v>
+        <v>117939970</v>
       </c>
       <c r="B9" t="n">
-        <v>100017</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1425,17 +1395,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bispgården (Bispgården), Jmt</t>
+          <t>Bispgården, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582214</v>
+        <v>582114</v>
       </c>
       <c r="R9" t="n">
-        <v>6989217</v>
+        <v>6989205</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1491,53 +1461,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117958577</v>
+        <v>117940181</v>
       </c>
       <c r="B10" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bispgården (Bispgården), Jmt</t>
+          <t>Bispgården, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582146</v>
+        <v>582118</v>
       </c>
       <c r="R10" t="n">
-        <v>6989221</v>
+        <v>6989264</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1561,22 +1526,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,27 +1546,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117958501</v>
+        <v>117940323</v>
       </c>
       <c r="B11" t="n">
-        <v>90515</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,37 +1569,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1205</v>
+        <v>222771</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bispgården (Bispgården), Jmt</t>
+          <t>Bispgården, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582151</v>
+        <v>582162</v>
       </c>
       <c r="R11" t="n">
-        <v>6989251</v>
+        <v>6989239</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1673,12 +1623,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,15 +1643,500 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>117940358</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bispgården, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>582144</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6989238</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>117940397</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bispgården, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>582193</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6989205</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>117940604</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bispgården, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>582240</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6989227</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>117940646</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bispgården, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>582233</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6989261</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>117940714</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bispgården, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>582214</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6989217</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15836-2024 artfynd.xlsx
+++ b/artfynd/A 15836-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117958501</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117958577</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117939351</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117939819</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117940958</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118622632</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117939659</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117939970</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117940181</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117940323</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117940358</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117940397</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117940604</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117940646</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,8 +2212,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117940714</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>